--- a/Estatistica_Descritiva/df_baseED.xlsx
+++ b/Estatistica_Descritiva/df_baseED.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA315"/>
+  <dimension ref="A1:AC315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,16 @@
           <t>Ano de Criação</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>TotalDesmat</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>%Desmat</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -625,6 +635,12 @@
       </c>
       <c r="AA2" t="n">
         <v>1989</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>190.93</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.9217138028588714</v>
       </c>
     </row>
     <row r="3">
@@ -725,6 +741,12 @@
       <c r="AA3" t="n">
         <v>2006</v>
       </c>
+      <c r="AB3" t="n">
+        <v>67601.03694800001</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3.313230317830075</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -824,6 +846,12 @@
       <c r="AA4" t="n">
         <v>2016</v>
       </c>
+      <c r="AB4" t="n">
+        <v>187.31938</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1231290755280535</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -923,6 +951,12 @@
       <c r="AA5" t="n">
         <v>1985</v>
       </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1022,6 +1056,12 @@
       <c r="AA6" t="n">
         <v>2014</v>
       </c>
+      <c r="AB6" t="n">
+        <v>334.90997</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.05024484166278528</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1121,6 +1161,12 @@
       <c r="AA7" t="n">
         <v>2005</v>
       </c>
+      <c r="AB7" t="n">
+        <v>18529.701235</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5493289133973157</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1220,6 +1266,12 @@
       <c r="AA8" t="n">
         <v>2001</v>
       </c>
+      <c r="AB8" t="n">
+        <v>104.61</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.05728678497964731</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1319,6 +1371,12 @@
       <c r="AA9" t="n">
         <v>1983</v>
       </c>
+      <c r="AB9" t="n">
+        <v>21.873522</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.007555302937289891</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1418,6 +1476,12 @@
       <c r="AA10" t="n">
         <v>1981</v>
       </c>
+      <c r="AB10" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.01126957159768179</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1517,6 +1581,12 @@
       <c r="AA11" t="n">
         <v>1981</v>
       </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1616,6 +1686,12 @@
       <c r="AA12" t="n">
         <v>1982</v>
       </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1715,6 +1791,12 @@
       <c r="AA13" t="n">
         <v>1983</v>
       </c>
+      <c r="AB13" t="n">
+        <v>1597.438445</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.1921499964952543</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1814,6 +1896,12 @@
       <c r="AA14" t="n">
         <v>1985</v>
       </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1913,6 +2001,12 @@
       <c r="AA15" t="n">
         <v>1998</v>
       </c>
+      <c r="AB15" t="n">
+        <v>31219.12716800001</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.315955006638815</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -2012,6 +2106,12 @@
       <c r="AA16" t="n">
         <v>2005</v>
       </c>
+      <c r="AB16" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.003593316592188586</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2111,6 +2211,12 @@
       <c r="AA17" t="n">
         <v>2005</v>
       </c>
+      <c r="AB17" t="n">
+        <v>716.8105</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.0674991003514312</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2210,6 +2316,12 @@
       <c r="AA18" t="n">
         <v>1998</v>
       </c>
+      <c r="AB18" t="n">
+        <v>1531.514774</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.4621730792427332</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2309,6 +2421,12 @@
       <c r="AA19" t="n">
         <v>1961</v>
       </c>
+      <c r="AB19" t="n">
+        <v>1463.069448</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.4601633522084047</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2408,6 +2526,12 @@
       <c r="AA20" t="n">
         <v>1998</v>
       </c>
+      <c r="AB20" t="n">
+        <v>68.212389</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.01431232002276792</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2507,6 +2631,12 @@
       <c r="AA21" t="n">
         <v>1998</v>
       </c>
+      <c r="AB21" t="n">
+        <v>588.8984210000001</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.276365512429729</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2606,6 +2736,12 @@
       <c r="AA22" t="n">
         <v>1998</v>
       </c>
+      <c r="AB22" t="n">
+        <v>10749.976535</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.702704075101795</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2705,6 +2841,12 @@
       <c r="AA23" t="n">
         <v>2004</v>
       </c>
+      <c r="AB23" t="n">
+        <v>325.178714</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.1472592527090266</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2804,6 +2946,12 @@
       <c r="AA24" t="n">
         <v>2001</v>
       </c>
+      <c r="AB24" t="n">
+        <v>185.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.08610738971855035</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2903,6 +3051,12 @@
       <c r="AA25" t="n">
         <v>2001</v>
       </c>
+      <c r="AB25" t="n">
+        <v>226.966073</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.02341244699476014</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -3002,6 +3156,12 @@
       <c r="AA26" t="n">
         <v>1989</v>
       </c>
+      <c r="AB26" t="n">
+        <v>1631.867167</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.9623623230983968</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -3101,6 +3261,12 @@
       <c r="AA27" t="n">
         <v>2001</v>
       </c>
+      <c r="AB27" t="n">
+        <v>799.3373960000001</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.3452063975037418</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -3200,6 +3366,12 @@
       <c r="AA28" t="n">
         <v>2001</v>
       </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -3299,6 +3471,12 @@
       <c r="AA29" t="n">
         <v>1989</v>
       </c>
+      <c r="AB29" t="n">
+        <v>6700.371281000001</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.518964639216416</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -3398,6 +3576,12 @@
       <c r="AA30" t="n">
         <v>1989</v>
       </c>
+      <c r="AB30" t="n">
+        <v>5072.926152</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.5863851102248461</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -3497,6 +3681,12 @@
       <c r="AA31" t="n">
         <v>2016</v>
       </c>
+      <c r="AB31" t="n">
+        <v>2969.326886</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.5524272701684022</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -3596,6 +3786,12 @@
       <c r="AA32" t="n">
         <v>2006</v>
       </c>
+      <c r="AB32" t="n">
+        <v>7175.847644999999</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.05124010703197</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -3695,6 +3891,12 @@
       <c r="AA33" t="n">
         <v>1989</v>
       </c>
+      <c r="AB33" t="n">
+        <v>25.64</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.005605027397211757</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -3794,6 +3996,12 @@
       <c r="AA34" t="n">
         <v>1989</v>
       </c>
+      <c r="AB34" t="n">
+        <v>953.805708</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.04910657569274179</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -3893,6 +4101,12 @@
       <c r="AA35" t="n">
         <v>2016</v>
       </c>
+      <c r="AB35" t="n">
+        <v>2203.133576</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.2933711852800675</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -3992,6 +4206,12 @@
       <c r="AA36" t="n">
         <v>1988</v>
       </c>
+      <c r="AB36" t="n">
+        <v>6697.696565</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>6.810063118573205</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -4091,6 +4311,12 @@
       <c r="AA37" t="n">
         <v>2006</v>
       </c>
+      <c r="AB37" t="n">
+        <v>2007.715957</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.2711696762432362</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -4190,6 +4416,12 @@
       <c r="AA38" t="n">
         <v>2008</v>
       </c>
+      <c r="AB38" t="n">
+        <v>1949.622511</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.1326112027425171</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -4289,6 +4521,12 @@
       <c r="AA39" t="n">
         <v>1998</v>
       </c>
+      <c r="AB39" t="n">
+        <v>1313.500751</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.420539158633717</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -4388,6 +4626,12 @@
       <c r="AA40" t="n">
         <v>2006</v>
       </c>
+      <c r="AB40" t="n">
+        <v>115905.689971</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>8.905103082289244</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -4487,6 +4731,12 @@
       <c r="AA41" t="n">
         <v>1984</v>
       </c>
+      <c r="AB41" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.1731754577563884</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -4586,6 +4836,12 @@
       <c r="AA42" t="n">
         <v>2002</v>
       </c>
+      <c r="AB42" t="n">
+        <v>57.899269</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.01019487548069212</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -4685,6 +4941,12 @@
       <c r="AA43" t="n">
         <v>1988</v>
       </c>
+      <c r="AB43" t="n">
+        <v>43.28</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0.02453964039539319</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -4784,6 +5046,12 @@
       <c r="AA44" t="n">
         <v>2023</v>
       </c>
+      <c r="AB44" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0.01449528327641245</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -4883,6 +5151,12 @@
       <c r="AA45" t="n">
         <v>1988</v>
       </c>
+      <c r="AB45" t="n">
+        <v>455.862066</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0.1779840217799701</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4982,6 +5256,12 @@
       <c r="AA46" t="n">
         <v>1974</v>
       </c>
+      <c r="AB46" t="n">
+        <v>595.646689</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.1134443933611277</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -5081,6 +5361,12 @@
       <c r="AA47" t="n">
         <v>1989</v>
       </c>
+      <c r="AB47" t="n">
+        <v>2925.674451</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.491308198800064</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -5180,6 +5466,12 @@
       <c r="AA48" t="n">
         <v>2006</v>
       </c>
+      <c r="AB48" t="n">
+        <v>1480.850349</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0.5750337111533893</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -5279,6 +5571,12 @@
       <c r="AA49" t="n">
         <v>1989</v>
       </c>
+      <c r="AB49" t="n">
+        <v>106.172003</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0.02878570785316611</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -5378,6 +5676,12 @@
       <c r="AA50" t="n">
         <v>1985</v>
       </c>
+      <c r="AB50" t="n">
+        <v>1478.223474</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0.1386325747462115</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -5477,6 +5781,12 @@
       <c r="AA51" t="n">
         <v>1989</v>
       </c>
+      <c r="AB51" t="n">
+        <v>2836.609347</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0.3386767050352121</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -5576,6 +5886,12 @@
       <c r="AA52" t="n">
         <v>2005</v>
       </c>
+      <c r="AB52" t="n">
+        <v>905.5176409999999</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0.2032995759059235</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -5675,6 +5991,12 @@
       <c r="AA53" t="n">
         <v>1981</v>
       </c>
+      <c r="AB53" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0.006155820694962552</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -5774,6 +6096,12 @@
       <c r="AA54" t="n">
         <v>1979</v>
       </c>
+      <c r="AB54" t="n">
+        <v>729.591675</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0.1033244577460676</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -5873,6 +6201,12 @@
       <c r="AA55" t="n">
         <v>2016</v>
       </c>
+      <c r="AB55" t="n">
+        <v>326.310096</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0.03640888849625898</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -5972,6 +6306,12 @@
       <c r="AA56" t="n">
         <v>1980</v>
       </c>
+      <c r="AB56" t="n">
+        <v>169.61</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0.02580276383981511</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -6071,6 +6411,12 @@
       <c r="AA57" t="n">
         <v>2006</v>
       </c>
+      <c r="AB57" t="n">
+        <v>7899.03734</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0.9154142257427823</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -6170,6 +6516,12 @@
       <c r="AA58" t="n">
         <v>1980</v>
       </c>
+      <c r="AB58" t="n">
+        <v>441.0863410000001</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0.01863214442504154</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -6269,6 +6621,12 @@
       <c r="AA59" t="n">
         <v>2006</v>
       </c>
+      <c r="AB59" t="n">
+        <v>881.3451009999999</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0.04503487996270439</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -6368,6 +6726,12 @@
       <c r="AA60" t="n">
         <v>1989</v>
       </c>
+      <c r="AB60" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0.06076203039563301</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -6467,6 +6831,12 @@
       <c r="AA61" t="n">
         <v>1979</v>
       </c>
+      <c r="AB61" t="n">
+        <v>852.3086499999998</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0.0378398367596866</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6566,6 +6936,12 @@
       <c r="AA62" t="n">
         <v>2006</v>
       </c>
+      <c r="AB62" t="n">
+        <v>2375.928768</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0.441528610821902</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -6665,6 +7041,12 @@
       <c r="AA63" t="n">
         <v>1998</v>
       </c>
+      <c r="AB63" t="n">
+        <v>25.933417</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0.00922955459774741</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -6764,6 +7146,12 @@
       <c r="AA64" t="n">
         <v>2006</v>
       </c>
+      <c r="AB64" t="n">
+        <v>2950.41717</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0.3069151321085722</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -6863,6 +7251,12 @@
       <c r="AA65" t="n">
         <v>2017</v>
       </c>
+      <c r="AB65" t="n">
+        <v>386.14</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0.4895946012269279</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -6962,6 +7356,12 @@
       <c r="AA66" t="n">
         <v>2008</v>
       </c>
+      <c r="AB66" t="n">
+        <v>5877.056858</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0.330743310106072</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -7061,6 +7461,12 @@
       <c r="AA67" t="n">
         <v>2002</v>
       </c>
+      <c r="AB67" t="n">
+        <v>159.321415</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0.004121978470267877</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -7160,6 +7566,12 @@
       <c r="AA68" t="n">
         <v>2008</v>
       </c>
+      <c r="AB68" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0.002509279330010015</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -7259,6 +7671,12 @@
       <c r="AA69" t="n">
         <v>2001</v>
       </c>
+      <c r="AB69" t="n">
+        <v>116.460504</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0.04107950774379967</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -7358,6 +7776,12 @@
       <c r="AA70" t="n">
         <v>1998</v>
       </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -7457,6 +7881,12 @@
       <c r="AA71" t="n">
         <v>2005</v>
       </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -7556,6 +7986,12 @@
       <c r="AA72" t="n">
         <v>1982</v>
       </c>
+      <c r="AB72" t="n">
+        <v>141.04</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0.06275557280664525</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -7655,6 +8091,12 @@
       <c r="AA73" t="n">
         <v>1982</v>
       </c>
+      <c r="AB73" t="n">
+        <v>316.6300000000001</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0.05141797925068398</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -7754,6 +8196,12 @@
       <c r="AA74" t="n">
         <v>1961</v>
       </c>
+      <c r="AB74" t="n">
+        <v>13746.666662</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>5.063880222651536</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -7853,6 +8301,12 @@
       <c r="AA75" t="n">
         <v>1961</v>
       </c>
+      <c r="AB75" t="n">
+        <v>432.635497</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1247286788725701</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -7952,6 +8406,12 @@
       <c r="AA76" t="n">
         <v>1984</v>
       </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -8051,6 +8511,12 @@
       <c r="AA77" t="n">
         <v>2016</v>
       </c>
+      <c r="AB77" t="n">
+        <v>79.39</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>0.02210537112427541</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -8150,6 +8616,12 @@
       <c r="AA78" t="n">
         <v>1979</v>
       </c>
+      <c r="AB78" t="n">
+        <v>153.14038</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>0.03755683282858825</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -8249,6 +8721,12 @@
       <c r="AA79" t="n">
         <v>1989</v>
       </c>
+      <c r="AB79" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>0.001641947967421247</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -8348,6 +8826,12 @@
       <c r="AA80" t="n">
         <v>1990</v>
       </c>
+      <c r="AB80" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>0.004907293926534165</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -8447,6 +8931,12 @@
       <c r="AA81" t="n">
         <v>2005</v>
       </c>
+      <c r="AB81" t="n">
+        <v>13106.381708</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>3.830083108176632</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -8546,6 +9036,12 @@
       <c r="AA82" t="n">
         <v>2018</v>
       </c>
+      <c r="AB82" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>0.005001703546071773</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -8645,6 +9141,12 @@
       <c r="AA83" t="n">
         <v>2006</v>
       </c>
+      <c r="AB83" t="n">
+        <v>1491.152811</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>1.115247549431431</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -8744,6 +9246,12 @@
       <c r="AA84" t="n">
         <v>2005</v>
       </c>
+      <c r="AB84" t="n">
+        <v>2089.446757000001</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>2.492844191355688</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -8843,6 +9351,12 @@
       <c r="AA85" t="n">
         <v>2001</v>
       </c>
+      <c r="AB85" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>0.1188981458824654</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -8942,6 +9456,12 @@
       <c r="AA86" t="n">
         <v>2018</v>
       </c>
+      <c r="AB86" t="n">
+        <v>52.757601</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>0.009086356123863614</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -9041,6 +9561,12 @@
       <c r="AA87" t="n">
         <v>2001</v>
       </c>
+      <c r="AB87" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0.007241244732680057</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -9140,6 +9666,12 @@
       <c r="AA88" t="n">
         <v>1990</v>
       </c>
+      <c r="AB88" t="n">
+        <v>50686.01401799999</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>5.441152772712335</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -9239,6 +9771,12 @@
       <c r="AA89" t="n">
         <v>2002</v>
       </c>
+      <c r="AB89" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>0.5436928165032234</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -9338,6 +9876,12 @@
       <c r="AA90" t="n">
         <v>2018</v>
       </c>
+      <c r="AB90" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>0.03768632262680179</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -9433,6 +9977,8 @@
       <c r="AA91" t="n">
         <v>2018</v>
       </c>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -9532,6 +10078,14 @@
       <c r="AA92" t="n">
         <v>1992</v>
       </c>
+      <c r="AB92" t="n">
+        <v>24.032895</v>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -9627,6 +10181,8 @@
       <c r="AA93" t="n">
         <v>1992</v>
       </c>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -9726,6 +10282,12 @@
       <c r="AA94" t="n">
         <v>2004</v>
       </c>
+      <c r="AB94" t="n">
+        <v>33.12</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>0.01780133171484789</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -9825,6 +10387,12 @@
       <c r="AA95" t="n">
         <v>2006</v>
       </c>
+      <c r="AB95" t="n">
+        <v>320.99</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>0.2205191589187291</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -9924,6 +10492,12 @@
       <c r="AA96" t="n">
         <v>2002</v>
       </c>
+      <c r="AB96" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>0.3742517648405108</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -10023,6 +10597,12 @@
       <c r="AA97" t="n">
         <v>1990</v>
       </c>
+      <c r="AB97" t="n">
+        <v>9126.516099000002</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>1.696550183030036</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -10122,6 +10702,12 @@
       <c r="AA98" t="n">
         <v>2000</v>
       </c>
+      <c r="AB98" t="n">
+        <v>2393.078236</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>1.552611406479103</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -10221,6 +10807,12 @@
       <c r="AA99" t="n">
         <v>2001</v>
       </c>
+      <c r="AB99" t="n">
+        <v>519.395346</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>0.2917326036682311</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -10320,6 +10912,12 @@
       <c r="AA100" t="n">
         <v>2002</v>
       </c>
+      <c r="AB100" t="n">
+        <v>3434.595979</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>0.4537555247324018</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -10419,6 +11017,12 @@
       <c r="AA101" t="n">
         <v>1992</v>
       </c>
+      <c r="AB101" t="n">
+        <v>233.45</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>2.879760041197456</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -10514,6 +11118,8 @@
       <c r="AA102" t="n">
         <v>1992</v>
       </c>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -10613,6 +11219,12 @@
       <c r="AA103" t="n">
         <v>1992</v>
       </c>
+      <c r="AB103" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>0.006835585234475928</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -10712,6 +11324,12 @@
       <c r="AA104" t="n">
         <v>2004</v>
       </c>
+      <c r="AB104" t="n">
+        <v>414.7897170000001</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>0.1359633572269963</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -10811,6 +11429,12 @@
       <c r="AA105" t="n">
         <v>2018</v>
       </c>
+      <c r="AB105" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>0.01782488303108411</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -10910,6 +11534,12 @@
       <c r="AA106" t="n">
         <v>1997</v>
       </c>
+      <c r="AB106" t="n">
+        <v>351.3600000000001</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>0.1224443087313087</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -11009,6 +11639,12 @@
       <c r="AA107" t="n">
         <v>2008</v>
       </c>
+      <c r="AB107" t="n">
+        <v>1300.490797</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0.2165509294918997</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -11108,6 +11744,12 @@
       <c r="AA108" t="n">
         <v>1992</v>
       </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -11207,6 +11849,12 @@
       <c r="AA109" t="n">
         <v>1990</v>
       </c>
+      <c r="AB109" t="n">
+        <v>3991.199658999999</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0.7496707933569663</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -11306,6 +11954,12 @@
       <c r="AA110" t="n">
         <v>2001</v>
       </c>
+      <c r="AB110" t="n">
+        <v>442.03</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0.5888950097217529</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -11405,6 +12059,12 @@
       <c r="AA111" t="n">
         <v>2002</v>
       </c>
+      <c r="AB111" t="n">
+        <v>501.95288</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0.1821873725291004</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -11504,6 +12164,12 @@
       <c r="AA112" t="n">
         <v>1990</v>
       </c>
+      <c r="AB112" t="n">
+        <v>3416.189232</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>1.669442542200658</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -11603,6 +12269,12 @@
       <c r="AA113" t="n">
         <v>2005</v>
       </c>
+      <c r="AB113" t="n">
+        <v>1211.1135</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>2.169112919391283</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -11702,6 +12374,12 @@
       <c r="AA114" t="n">
         <v>2018</v>
       </c>
+      <c r="AB114" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>0.04694974228952286</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -11801,6 +12479,12 @@
       <c r="AA115" t="n">
         <v>2008</v>
       </c>
+      <c r="AB115" t="n">
+        <v>895.1740229999999</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>0.1155403519622897</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -11900,6 +12584,12 @@
       <c r="AA116" t="n">
         <v>2002</v>
       </c>
+      <c r="AB116" t="n">
+        <v>34.86000000000001</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>0.09504144013694589</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -11999,6 +12689,12 @@
       <c r="AA117" t="n">
         <v>2005</v>
       </c>
+      <c r="AB117" t="n">
+        <v>294.1208350000001</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.3137001853530243</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -12098,6 +12794,12 @@
       <c r="AA118" t="n">
         <v>2002</v>
       </c>
+      <c r="AB118" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.1672658289197984</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -12197,6 +12899,12 @@
       <c r="AA119" t="n">
         <v>2014</v>
       </c>
+      <c r="AB119" t="n">
+        <v>64.414556</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.5846838396990037</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -12296,6 +13004,12 @@
       <c r="AA120" t="n">
         <v>2005</v>
       </c>
+      <c r="AB120" t="n">
+        <v>75.92583500000001</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.12182676840058</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -12395,6 +13109,12 @@
       <c r="AA121" t="n">
         <v>2005</v>
       </c>
+      <c r="AB121" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.07180596377770275</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -12494,6 +13214,12 @@
       <c r="AA122" t="n">
         <v>2005</v>
       </c>
+      <c r="AB122" t="n">
+        <v>67.05</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.09211530456702115</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -12593,6 +13319,12 @@
       <c r="AA123" t="n">
         <v>2001</v>
       </c>
+      <c r="AB123" t="n">
+        <v>108.01</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.3651630028654451</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -12692,6 +13424,12 @@
       <c r="AA124" t="n">
         <v>2005</v>
       </c>
+      <c r="AB124" t="n">
+        <v>27.58</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.0989799522862618</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -12791,6 +13529,12 @@
       <c r="AA125" t="n">
         <v>2014</v>
       </c>
+      <c r="AB125" t="n">
+        <v>119.14</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.4502596288213043</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -12890,6 +13634,12 @@
       <c r="AA126" t="n">
         <v>2014</v>
       </c>
+      <c r="AB126" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.1790813478414685</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -12989,6 +13739,12 @@
       <c r="AA127" t="n">
         <v>2009</v>
       </c>
+      <c r="AB127" t="n">
+        <v>4836.58947</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>2.307322039187631</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -13088,6 +13844,12 @@
       <c r="AA128" t="n">
         <v>2006</v>
       </c>
+      <c r="AB128" t="n">
+        <v>948.7851640000001</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.2384167962026412</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -13187,6 +13949,12 @@
       <c r="AA129" t="n">
         <v>2006</v>
       </c>
+      <c r="AB129" t="n">
+        <v>177.982801</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.02117542271254528</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -13286,6 +14054,12 @@
       <c r="AA130" t="n">
         <v>2008</v>
       </c>
+      <c r="AB130" t="n">
+        <v>165.05</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.05448252717663084</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -13385,6 +14159,12 @@
       <c r="AA131" t="n">
         <v>2005</v>
       </c>
+      <c r="AB131" t="n">
+        <v>2067.761573</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.6371532177091437</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -13484,6 +14264,12 @@
       <c r="AA132" t="n">
         <v>2004</v>
       </c>
+      <c r="AB132" t="n">
+        <v>3709.498267</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.5033202668438141</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -13583,6 +14369,12 @@
       <c r="AA133" t="n">
         <v>1998</v>
       </c>
+      <c r="AB133" t="n">
+        <v>2114.287002</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.3121559579546383</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -13682,6 +14474,12 @@
       <c r="AA134" t="n">
         <v>2006</v>
       </c>
+      <c r="AB134" t="n">
+        <v>742.455779</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3810228935144547</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -13781,6 +14579,12 @@
       <c r="AA135" t="n">
         <v>2004</v>
       </c>
+      <c r="AB135" t="n">
+        <v>12430.176311</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.9640958454441342</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -13874,6 +14678,8 @@
       <c r="AA136" t="n">
         <v>1992</v>
       </c>
+      <c r="AB136" t="inlineStr"/>
+      <c r="AC136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -13967,6 +14773,8 @@
       <c r="AA137" t="n">
         <v>2010</v>
       </c>
+      <c r="AB137" t="inlineStr"/>
+      <c r="AC137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -14060,6 +14868,8 @@
       <c r="AA138" t="n">
         <v>1982</v>
       </c>
+      <c r="AB138" t="inlineStr"/>
+      <c r="AC138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -14153,6 +14963,8 @@
       <c r="AA139" t="n">
         <v>2002</v>
       </c>
+      <c r="AB139" t="inlineStr"/>
+      <c r="AC139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -14246,6 +15058,8 @@
       <c r="AA140" t="n">
         <v>2000</v>
       </c>
+      <c r="AB140" t="inlineStr"/>
+      <c r="AC140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -14339,6 +15153,8 @@
       <c r="AA141" t="n">
         <v>1993</v>
       </c>
+      <c r="AB141" t="inlineStr"/>
+      <c r="AC141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -14432,6 +15248,8 @@
       <c r="AA142" t="n">
         <v>1993</v>
       </c>
+      <c r="AB142" t="inlineStr"/>
+      <c r="AC142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -14525,6 +15343,8 @@
       <c r="AA143" t="n">
         <v>1997</v>
       </c>
+      <c r="AB143" t="inlineStr"/>
+      <c r="AC143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -14618,6 +15438,8 @@
       <c r="AA144" t="n">
         <v>1982</v>
       </c>
+      <c r="AB144" t="inlineStr"/>
+      <c r="AC144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -14711,6 +15533,8 @@
       <c r="AA145" t="n">
         <v>1985</v>
       </c>
+      <c r="AB145" t="inlineStr"/>
+      <c r="AC145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -14804,6 +15628,8 @@
       <c r="AA146" t="n">
         <v>1997</v>
       </c>
+      <c r="AB146" t="inlineStr"/>
+      <c r="AC146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -14899,6 +15725,8 @@
       <c r="AA147" t="n">
         <v>1997</v>
       </c>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -14992,6 +15820,8 @@
       <c r="AA148" t="n">
         <v>1983</v>
       </c>
+      <c r="AB148" t="inlineStr"/>
+      <c r="AC148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -15085,6 +15915,8 @@
       <c r="AA149" t="n">
         <v>1995</v>
       </c>
+      <c r="AB149" t="inlineStr"/>
+      <c r="AC149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -15178,6 +16010,8 @@
       <c r="AA150" t="n">
         <v>1986</v>
       </c>
+      <c r="AB150" t="inlineStr"/>
+      <c r="AC150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -15271,6 +16105,8 @@
       <c r="AA151" t="n">
         <v>1984</v>
       </c>
+      <c r="AB151" t="inlineStr"/>
+      <c r="AC151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -15364,6 +16200,8 @@
       <c r="AA152" t="n">
         <v>1985</v>
       </c>
+      <c r="AB152" t="inlineStr"/>
+      <c r="AC152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -15457,6 +16295,8 @@
       <c r="AA153" t="n">
         <v>1983</v>
       </c>
+      <c r="AB153" t="inlineStr"/>
+      <c r="AC153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -15550,6 +16390,8 @@
       <c r="AA154" t="n">
         <v>1990</v>
       </c>
+      <c r="AB154" t="inlineStr"/>
+      <c r="AC154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -15645,6 +16487,8 @@
       <c r="AA155" t="n">
         <v>1990</v>
       </c>
+      <c r="AB155" t="inlineStr"/>
+      <c r="AC155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -15738,6 +16582,8 @@
       <c r="AA156" t="n">
         <v>1985</v>
       </c>
+      <c r="AB156" t="inlineStr"/>
+      <c r="AC156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -15831,6 +16677,8 @@
       <c r="AA157" t="n">
         <v>1985</v>
       </c>
+      <c r="AB157" t="inlineStr"/>
+      <c r="AC157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -15924,6 +16772,8 @@
       <c r="AA158" t="n">
         <v>1985</v>
       </c>
+      <c r="AB158" t="inlineStr"/>
+      <c r="AC158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -16017,6 +16867,8 @@
       <c r="AA159" t="n">
         <v>1985</v>
       </c>
+      <c r="AB159" t="inlineStr"/>
+      <c r="AC159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -16110,6 +16962,8 @@
       <c r="AA160" t="n">
         <v>1996</v>
       </c>
+      <c r="AB160" t="inlineStr"/>
+      <c r="AC160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -16203,6 +17057,8 @@
       <c r="AA161" t="n">
         <v>2005</v>
       </c>
+      <c r="AB161" t="inlineStr"/>
+      <c r="AC161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -16296,6 +17152,8 @@
       <c r="AA162" t="n">
         <v>1981</v>
       </c>
+      <c r="AB162" t="inlineStr"/>
+      <c r="AC162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -16389,6 +17247,8 @@
       <c r="AA163" t="n">
         <v>2001</v>
       </c>
+      <c r="AB163" t="inlineStr"/>
+      <c r="AC163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -16482,6 +17342,8 @@
       <c r="AA164" t="n">
         <v>1990</v>
       </c>
+      <c r="AB164" t="inlineStr"/>
+      <c r="AC164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -16575,6 +17437,8 @@
       <c r="AA165" t="n">
         <v>2002</v>
       </c>
+      <c r="AB165" t="inlineStr"/>
+      <c r="AC165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -16668,6 +17532,8 @@
       <c r="AA166" t="n">
         <v>1968</v>
       </c>
+      <c r="AB166" t="inlineStr"/>
+      <c r="AC166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -16761,6 +17627,8 @@
       <c r="AA167" t="n">
         <v>1968</v>
       </c>
+      <c r="AB167" t="inlineStr"/>
+      <c r="AC167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -16854,6 +17722,8 @@
       <c r="AA168" t="n">
         <v>1968</v>
       </c>
+      <c r="AB168" t="inlineStr"/>
+      <c r="AC168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -16949,6 +17819,8 @@
       <c r="AA169" t="n">
         <v>1968</v>
       </c>
+      <c r="AB169" t="inlineStr"/>
+      <c r="AC169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -17042,6 +17914,8 @@
       <c r="AA170" t="n">
         <v>1968</v>
       </c>
+      <c r="AB170" t="inlineStr"/>
+      <c r="AC170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -17135,6 +18009,8 @@
       <c r="AA171" t="n">
         <v>2012</v>
       </c>
+      <c r="AB171" t="inlineStr"/>
+      <c r="AC171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -17228,6 +18104,8 @@
       <c r="AA172" t="n">
         <v>1988</v>
       </c>
+      <c r="AB172" t="inlineStr"/>
+      <c r="AC172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -17321,6 +18199,8 @@
       <c r="AA173" t="n">
         <v>1992</v>
       </c>
+      <c r="AB173" t="inlineStr"/>
+      <c r="AC173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -17414,6 +18294,8 @@
       <c r="AA174" t="n">
         <v>1968</v>
       </c>
+      <c r="AB174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -17507,6 +18389,8 @@
       <c r="AA175" t="n">
         <v>1934</v>
       </c>
+      <c r="AB175" t="inlineStr"/>
+      <c r="AC175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -17600,6 +18484,8 @@
       <c r="AA176" t="n">
         <v>2001</v>
       </c>
+      <c r="AB176" t="inlineStr"/>
+      <c r="AC176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -17693,6 +18579,8 @@
       <c r="AA177" t="n">
         <v>2002</v>
       </c>
+      <c r="AB177" t="inlineStr"/>
+      <c r="AC177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -17786,6 +18674,8 @@
       <c r="AA178" t="n">
         <v>1968</v>
       </c>
+      <c r="AB178" t="inlineStr"/>
+      <c r="AC178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -17879,6 +18769,8 @@
       <c r="AA179" t="n">
         <v>2004</v>
       </c>
+      <c r="AB179" t="inlineStr"/>
+      <c r="AC179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -17972,6 +18864,8 @@
       <c r="AA180" t="n">
         <v>1999</v>
       </c>
+      <c r="AB180" t="inlineStr"/>
+      <c r="AC180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -18065,6 +18959,8 @@
       <c r="AA181" t="n">
         <v>1968</v>
       </c>
+      <c r="AB181" t="inlineStr"/>
+      <c r="AC181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -18158,6 +19054,8 @@
       <c r="AA182" t="n">
         <v>1968</v>
       </c>
+      <c r="AB182" t="inlineStr"/>
+      <c r="AC182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -18251,6 +19149,8 @@
       <c r="AA183" t="n">
         <v>2005</v>
       </c>
+      <c r="AB183" t="inlineStr"/>
+      <c r="AC183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -18344,6 +19244,8 @@
       <c r="AA184" t="n">
         <v>1990</v>
       </c>
+      <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -18437,6 +19339,8 @@
       <c r="AA185" t="n">
         <v>1986</v>
       </c>
+      <c r="AB185" t="inlineStr"/>
+      <c r="AC185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -18530,6 +19434,8 @@
       <c r="AA186" t="n">
         <v>2008</v>
       </c>
+      <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -18623,6 +19529,8 @@
       <c r="AA187" t="n">
         <v>1998</v>
       </c>
+      <c r="AB187" t="inlineStr"/>
+      <c r="AC187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -18716,6 +19624,8 @@
       <c r="AA188" t="n">
         <v>1972</v>
       </c>
+      <c r="AB188" t="inlineStr"/>
+      <c r="AC188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -18809,6 +19719,8 @@
       <c r="AA189" t="n">
         <v>2010</v>
       </c>
+      <c r="AB189" t="inlineStr"/>
+      <c r="AC189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -18902,6 +19814,8 @@
       <c r="AA190" t="n">
         <v>1984</v>
       </c>
+      <c r="AB190" t="inlineStr"/>
+      <c r="AC190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -18997,6 +19911,8 @@
       <c r="AA191" t="n">
         <v>1984</v>
       </c>
+      <c r="AB191" t="inlineStr"/>
+      <c r="AC191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -19090,6 +20006,8 @@
       <c r="AA192" t="n">
         <v>2014</v>
       </c>
+      <c r="AB192" t="inlineStr"/>
+      <c r="AC192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -19183,6 +20101,8 @@
       <c r="AA193" t="n">
         <v>2004</v>
       </c>
+      <c r="AB193" t="inlineStr"/>
+      <c r="AC193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -19276,6 +20196,8 @@
       <c r="AA194" t="n">
         <v>1939</v>
       </c>
+      <c r="AB194" t="inlineStr"/>
+      <c r="AC194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -19369,6 +20291,8 @@
       <c r="AA195" t="n">
         <v>1992</v>
       </c>
+      <c r="AB195" t="inlineStr"/>
+      <c r="AC195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -19462,6 +20386,8 @@
       <c r="AA196" t="n">
         <v>1972</v>
       </c>
+      <c r="AB196" t="inlineStr"/>
+      <c r="AC196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -19555,6 +20481,8 @@
       <c r="AA197" t="n">
         <v>2005</v>
       </c>
+      <c r="AB197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -19648,6 +20576,8 @@
       <c r="AA198" t="n">
         <v>1972</v>
       </c>
+      <c r="AB198" t="inlineStr"/>
+      <c r="AC198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -19741,6 +20671,8 @@
       <c r="AA199" t="n">
         <v>2010</v>
       </c>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -19834,6 +20766,8 @@
       <c r="AA200" t="n">
         <v>2010</v>
       </c>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -19927,6 +20861,8 @@
       <c r="AA201" t="n">
         <v>1997</v>
       </c>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -20020,6 +20956,8 @@
       <c r="AA202" t="n">
         <v>1937</v>
       </c>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -20113,6 +21051,8 @@
       <c r="AA203" t="n">
         <v>2001</v>
       </c>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -20206,6 +21146,8 @@
       <c r="AA204" t="n">
         <v>2016</v>
       </c>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -20299,6 +21241,8 @@
       <c r="AA205" t="n">
         <v>2010</v>
       </c>
+      <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -20392,6 +21336,8 @@
       <c r="AA206" t="n">
         <v>1961</v>
       </c>
+      <c r="AB206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -20485,6 +21431,8 @@
       <c r="AA207" t="n">
         <v>1999</v>
       </c>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -20578,6 +21526,8 @@
       <c r="AA208" t="n">
         <v>1939</v>
       </c>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -20671,6 +21621,8 @@
       <c r="AA209" t="n">
         <v>2010</v>
       </c>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -20764,6 +21716,8 @@
       <c r="AA210" t="n">
         <v>2006</v>
       </c>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -20857,6 +21811,8 @@
       <c r="AA211" t="n">
         <v>1961</v>
       </c>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -20950,6 +21906,8 @@
       <c r="AA212" t="n">
         <v>2014</v>
       </c>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -21043,6 +22001,8 @@
       <c r="AA213" t="n">
         <v>1988</v>
       </c>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -21136,6 +22096,8 @@
       <c r="AA214" t="n">
         <v>2005</v>
       </c>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -21229,6 +22191,8 @@
       <c r="AA215" t="n">
         <v>2005</v>
       </c>
+      <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -21322,6 +22286,8 @@
       <c r="AA216" t="n">
         <v>1982</v>
       </c>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -21415,6 +22381,8 @@
       <c r="AA217" t="n">
         <v>2012</v>
       </c>
+      <c r="AB217" t="inlineStr"/>
+      <c r="AC217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -21508,6 +22476,8 @@
       <c r="AA218" t="n">
         <v>2003</v>
       </c>
+      <c r="AB218" t="inlineStr"/>
+      <c r="AC218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -21601,6 +22571,8 @@
       <c r="AA219" t="n">
         <v>2006</v>
       </c>
+      <c r="AB219" t="inlineStr"/>
+      <c r="AC219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -21694,6 +22666,8 @@
       <c r="AA220" t="n">
         <v>2006</v>
       </c>
+      <c r="AB220" t="inlineStr"/>
+      <c r="AC220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -21787,6 +22761,8 @@
       <c r="AA221" t="n">
         <v>1989</v>
       </c>
+      <c r="AB221" t="inlineStr"/>
+      <c r="AC221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -21880,6 +22856,8 @@
       <c r="AA222" t="n">
         <v>1974</v>
       </c>
+      <c r="AB222" t="inlineStr"/>
+      <c r="AC222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -21973,6 +22951,8 @@
       <c r="AA223" t="n">
         <v>1983</v>
       </c>
+      <c r="AB223" t="inlineStr"/>
+      <c r="AC223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -22066,6 +23046,8 @@
       <c r="AA224" t="n">
         <v>1988</v>
       </c>
+      <c r="AB224" t="inlineStr"/>
+      <c r="AC224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -22159,6 +23141,8 @@
       <c r="AA225" t="n">
         <v>1982</v>
       </c>
+      <c r="AB225" t="inlineStr"/>
+      <c r="AC225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -22252,6 +23236,8 @@
       <c r="AA226" t="n">
         <v>1980</v>
       </c>
+      <c r="AB226" t="inlineStr"/>
+      <c r="AC226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -22345,6 +23331,8 @@
       <c r="AA227" t="n">
         <v>1984</v>
       </c>
+      <c r="AB227" t="inlineStr"/>
+      <c r="AC227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -22438,6 +23426,8 @@
       <c r="AA228" t="n">
         <v>1989</v>
       </c>
+      <c r="AB228" t="inlineStr"/>
+      <c r="AC228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -22531,6 +23521,8 @@
       <c r="AA229" t="n">
         <v>1990</v>
       </c>
+      <c r="AB229" t="inlineStr"/>
+      <c r="AC229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -22624,6 +23616,8 @@
       <c r="AA230" t="n">
         <v>1990</v>
       </c>
+      <c r="AB230" t="inlineStr"/>
+      <c r="AC230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -22717,6 +23711,8 @@
       <c r="AA231" t="n">
         <v>1998</v>
       </c>
+      <c r="AB231" t="inlineStr"/>
+      <c r="AC231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -22810,6 +23806,8 @@
       <c r="AA232" t="n">
         <v>2007</v>
       </c>
+      <c r="AB232" t="inlineStr"/>
+      <c r="AC232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -22903,6 +23901,8 @@
       <c r="AA233" t="n">
         <v>2006</v>
       </c>
+      <c r="AB233" t="inlineStr"/>
+      <c r="AC233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -22996,6 +23996,8 @@
       <c r="AA234" t="n">
         <v>2009</v>
       </c>
+      <c r="AB234" t="inlineStr"/>
+      <c r="AC234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -23089,6 +24091,8 @@
       <c r="AA235" t="n">
         <v>2000</v>
       </c>
+      <c r="AB235" t="inlineStr"/>
+      <c r="AC235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -23182,6 +24186,8 @@
       <c r="AA236" t="n">
         <v>2001</v>
       </c>
+      <c r="AB236" t="inlineStr"/>
+      <c r="AC236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -23275,6 +24281,8 @@
       <c r="AA237" t="n">
         <v>1997</v>
       </c>
+      <c r="AB237" t="inlineStr"/>
+      <c r="AC237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -23368,6 +24376,8 @@
       <c r="AA238" t="n">
         <v>2000</v>
       </c>
+      <c r="AB238" t="inlineStr"/>
+      <c r="AC238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -23461,6 +24471,8 @@
       <c r="AA239" t="n">
         <v>2010</v>
       </c>
+      <c r="AB239" t="inlineStr"/>
+      <c r="AC239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -23554,6 +24566,8 @@
       <c r="AA240" t="n">
         <v>2010</v>
       </c>
+      <c r="AB240" t="inlineStr"/>
+      <c r="AC240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -23647,6 +24661,8 @@
       <c r="AA241" t="n">
         <v>2007</v>
       </c>
+      <c r="AB241" t="inlineStr"/>
+      <c r="AC241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -23740,6 +24756,8 @@
       <c r="AA242" t="n">
         <v>2007</v>
       </c>
+      <c r="AB242" t="inlineStr"/>
+      <c r="AC242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -23833,6 +24851,8 @@
       <c r="AA243" t="n">
         <v>2006</v>
       </c>
+      <c r="AB243" t="inlineStr"/>
+      <c r="AC243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -23926,6 +24946,8 @@
       <c r="AA244" t="n">
         <v>1992</v>
       </c>
+      <c r="AB244" t="inlineStr"/>
+      <c r="AC244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -24019,6 +25041,8 @@
       <c r="AA245" t="n">
         <v>1986</v>
       </c>
+      <c r="AB245" t="inlineStr"/>
+      <c r="AC245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -24112,6 +25136,8 @@
       <c r="AA246" t="n">
         <v>1986</v>
       </c>
+      <c r="AB246" t="inlineStr"/>
+      <c r="AC246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -24207,6 +25233,8 @@
       <c r="AA247" t="n">
         <v>1990</v>
       </c>
+      <c r="AB247" t="inlineStr"/>
+      <c r="AC247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -24302,6 +25330,8 @@
       <c r="AA248" t="n">
         <v>1989</v>
       </c>
+      <c r="AB248" t="inlineStr"/>
+      <c r="AC248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -24395,6 +25425,8 @@
       <c r="AA249" t="n">
         <v>1989</v>
       </c>
+      <c r="AB249" t="inlineStr"/>
+      <c r="AC249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -24490,6 +25522,8 @@
       <c r="AA250" t="n">
         <v>1983</v>
       </c>
+      <c r="AB250" t="inlineStr"/>
+      <c r="AC250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -24585,6 +25619,8 @@
       <c r="AA251" t="n">
         <v>2001</v>
       </c>
+      <c r="AB251" t="inlineStr"/>
+      <c r="AC251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -24680,6 +25716,8 @@
       <c r="AA252" t="n">
         <v>1996</v>
       </c>
+      <c r="AB252" t="inlineStr"/>
+      <c r="AC252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -24773,6 +25811,8 @@
       <c r="AA253" t="n">
         <v>1996</v>
       </c>
+      <c r="AB253" t="inlineStr"/>
+      <c r="AC253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -24868,6 +25908,8 @@
       <c r="AA254" t="n">
         <v>2002</v>
       </c>
+      <c r="AB254" t="inlineStr"/>
+      <c r="AC254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -24963,6 +26005,8 @@
       <c r="AA255" t="n">
         <v>1998</v>
       </c>
+      <c r="AB255" t="inlineStr"/>
+      <c r="AC255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -25058,6 +26102,8 @@
       <c r="AA256" t="n">
         <v>1996</v>
       </c>
+      <c r="AB256" t="inlineStr"/>
+      <c r="AC256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -25151,6 +26197,8 @@
       <c r="AA257" t="n">
         <v>1996</v>
       </c>
+      <c r="AB257" t="inlineStr"/>
+      <c r="AC257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -25246,6 +26294,8 @@
       <c r="AA258" t="n">
         <v>2002</v>
       </c>
+      <c r="AB258" t="inlineStr"/>
+      <c r="AC258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -25341,6 +26391,8 @@
       <c r="AA259" t="n">
         <v>1990</v>
       </c>
+      <c r="AB259" t="inlineStr"/>
+      <c r="AC259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -25436,6 +26488,8 @@
       <c r="AA260" t="n">
         <v>1982</v>
       </c>
+      <c r="AB260" t="inlineStr"/>
+      <c r="AC260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -25531,6 +26585,8 @@
       <c r="AA261" t="n">
         <v>1981</v>
       </c>
+      <c r="AB261" t="inlineStr"/>
+      <c r="AC261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -25626,6 +26682,8 @@
       <c r="AA262" t="n">
         <v>2001</v>
       </c>
+      <c r="AB262" t="inlineStr"/>
+      <c r="AC262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -25721,6 +26779,8 @@
       <c r="AA263" t="n">
         <v>1999</v>
       </c>
+      <c r="AB263" t="inlineStr"/>
+      <c r="AC263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -25816,6 +26876,8 @@
       <c r="AA264" t="n">
         <v>2005</v>
       </c>
+      <c r="AB264" t="inlineStr"/>
+      <c r="AC264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -25911,6 +26973,8 @@
       <c r="AA265" t="n">
         <v>2001</v>
       </c>
+      <c r="AB265" t="inlineStr"/>
+      <c r="AC265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -26006,6 +27070,8 @@
       <c r="AA266" t="n">
         <v>2001</v>
       </c>
+      <c r="AB266" t="inlineStr"/>
+      <c r="AC266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -26101,6 +27167,8 @@
       <c r="AA267" t="n">
         <v>1999</v>
       </c>
+      <c r="AB267" t="inlineStr"/>
+      <c r="AC267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -26194,6 +27262,8 @@
       <c r="AA268" t="n">
         <v>1999</v>
       </c>
+      <c r="AB268" t="inlineStr"/>
+      <c r="AC268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -26289,6 +27359,8 @@
       <c r="AA269" t="n">
         <v>2006</v>
       </c>
+      <c r="AB269" t="inlineStr"/>
+      <c r="AC269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -26384,6 +27456,8 @@
       <c r="AA270" t="n">
         <v>1989</v>
       </c>
+      <c r="AB270" t="inlineStr"/>
+      <c r="AC270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -26479,6 +27553,8 @@
       <c r="AA271" t="n">
         <v>2000</v>
       </c>
+      <c r="AB271" t="inlineStr"/>
+      <c r="AC271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -26574,6 +27650,8 @@
       <c r="AA272" t="n">
         <v>1972</v>
       </c>
+      <c r="AB272" t="inlineStr"/>
+      <c r="AC272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -26669,6 +27747,8 @@
       <c r="AA273" t="n">
         <v>2010</v>
       </c>
+      <c r="AB273" t="inlineStr"/>
+      <c r="AC273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -26762,6 +27842,8 @@
       <c r="AA274" t="n">
         <v>2010</v>
       </c>
+      <c r="AB274" t="inlineStr"/>
+      <c r="AC274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -26857,6 +27939,8 @@
       <c r="AA275" t="n">
         <v>1972</v>
       </c>
+      <c r="AB275" t="inlineStr"/>
+      <c r="AC275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -26952,6 +28036,8 @@
       <c r="AA276" t="n">
         <v>2015</v>
       </c>
+      <c r="AB276" t="inlineStr"/>
+      <c r="AC276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -27047,6 +28133,8 @@
       <c r="AA277" t="n">
         <v>2002</v>
       </c>
+      <c r="AB277" t="inlineStr"/>
+      <c r="AC277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -27142,6 +28230,8 @@
       <c r="AA278" t="n">
         <v>1961</v>
       </c>
+      <c r="AB278" t="inlineStr"/>
+      <c r="AC278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -27237,6 +28327,8 @@
       <c r="AA279" t="n">
         <v>1961</v>
       </c>
+      <c r="AB279" t="inlineStr"/>
+      <c r="AC279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -27332,6 +28424,8 @@
       <c r="AA280" t="n">
         <v>1971</v>
       </c>
+      <c r="AB280" t="inlineStr"/>
+      <c r="AC280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -27427,6 +28521,8 @@
       <c r="AA281" t="n">
         <v>1981</v>
       </c>
+      <c r="AB281" t="inlineStr"/>
+      <c r="AC281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -27522,6 +28618,8 @@
       <c r="AA282" t="n">
         <v>1989</v>
       </c>
+      <c r="AB282" t="inlineStr"/>
+      <c r="AC282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -27617,6 +28715,8 @@
       <c r="AA283" t="n">
         <v>2014</v>
       </c>
+      <c r="AB283" t="inlineStr"/>
+      <c r="AC283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -27712,6 +28812,8 @@
       <c r="AA284" t="n">
         <v>2002</v>
       </c>
+      <c r="AB284" t="inlineStr"/>
+      <c r="AC284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -27807,6 +28909,8 @@
       <c r="AA285" t="n">
         <v>2007</v>
       </c>
+      <c r="AB285" t="inlineStr"/>
+      <c r="AC285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -27902,6 +29006,8 @@
       <c r="AA286" t="n">
         <v>2006</v>
       </c>
+      <c r="AB286" t="inlineStr"/>
+      <c r="AC286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -27997,6 +29103,8 @@
       <c r="AA287" t="n">
         <v>2006</v>
       </c>
+      <c r="AB287" t="inlineStr"/>
+      <c r="AC287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -28092,6 +29200,8 @@
       <c r="AA288" t="n">
         <v>2000</v>
       </c>
+      <c r="AB288" t="inlineStr"/>
+      <c r="AC288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -28187,6 +29297,8 @@
       <c r="AA289" t="n">
         <v>2002</v>
       </c>
+      <c r="AB289" t="inlineStr"/>
+      <c r="AC289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -28280,6 +29392,8 @@
       <c r="AA290" t="n">
         <v>2018</v>
       </c>
+      <c r="AB290" t="inlineStr"/>
+      <c r="AC290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -28373,6 +29487,8 @@
       <c r="AA291" t="n">
         <v>1997</v>
       </c>
+      <c r="AB291" t="inlineStr"/>
+      <c r="AC291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -28466,6 +29582,8 @@
       <c r="AA292" t="n">
         <v>2018</v>
       </c>
+      <c r="AB292" t="inlineStr"/>
+      <c r="AC292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -28559,6 +29677,8 @@
       <c r="AA293" t="n">
         <v>2008</v>
       </c>
+      <c r="AB293" t="inlineStr"/>
+      <c r="AC293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -28652,6 +29772,8 @@
       <c r="AA294" t="n">
         <v>2001</v>
       </c>
+      <c r="AB294" t="inlineStr"/>
+      <c r="AC294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -28745,6 +29867,8 @@
       <c r="AA295" t="n">
         <v>2001</v>
       </c>
+      <c r="AB295" t="inlineStr"/>
+      <c r="AC295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -28838,6 +29962,8 @@
       <c r="AA296" t="n">
         <v>1982</v>
       </c>
+      <c r="AB296" t="inlineStr"/>
+      <c r="AC296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -28931,6 +30057,8 @@
       <c r="AA297" t="n">
         <v>1984</v>
       </c>
+      <c r="AB297" t="inlineStr"/>
+      <c r="AC297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -29024,6 +30152,8 @@
       <c r="AA298" t="n">
         <v>1999</v>
       </c>
+      <c r="AB298" t="inlineStr"/>
+      <c r="AC298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -29117,6 +30247,8 @@
       <c r="AA299" t="n">
         <v>1950</v>
       </c>
+      <c r="AB299" t="inlineStr"/>
+      <c r="AC299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -29210,6 +30342,8 @@
       <c r="AA300" t="n">
         <v>2007</v>
       </c>
+      <c r="AB300" t="inlineStr"/>
+      <c r="AC300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -29303,6 +30437,8 @@
       <c r="AA301" t="n">
         <v>2001</v>
       </c>
+      <c r="AB301" t="inlineStr"/>
+      <c r="AC301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -29396,6 +30532,8 @@
       <c r="AA302" t="n">
         <v>1946</v>
       </c>
+      <c r="AB302" t="inlineStr"/>
+      <c r="AC302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -29489,6 +30627,8 @@
       <c r="AA303" t="n">
         <v>2009</v>
       </c>
+      <c r="AB303" t="inlineStr"/>
+      <c r="AC303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -29582,6 +30722,8 @@
       <c r="AA304" t="n">
         <v>1985</v>
       </c>
+      <c r="AB304" t="inlineStr"/>
+      <c r="AC304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -29675,6 +30817,8 @@
       <c r="AA305" t="n">
         <v>2012</v>
       </c>
+      <c r="AB305" t="inlineStr"/>
+      <c r="AC305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -29768,6 +30912,8 @@
       <c r="AA306" t="n">
         <v>1990</v>
       </c>
+      <c r="AB306" t="inlineStr"/>
+      <c r="AC306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -29861,6 +31007,8 @@
       <c r="AA307" t="n">
         <v>2023</v>
       </c>
+      <c r="AB307" t="inlineStr"/>
+      <c r="AC307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -29954,6 +31102,8 @@
       <c r="AA308" t="n">
         <v>2002</v>
       </c>
+      <c r="AB308" t="inlineStr"/>
+      <c r="AC308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -30047,6 +31197,8 @@
       <c r="AA309" t="n">
         <v>2002</v>
       </c>
+      <c r="AB309" t="inlineStr"/>
+      <c r="AC309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -30140,6 +31292,8 @@
       <c r="AA310" t="n">
         <v>2018</v>
       </c>
+      <c r="AB310" t="inlineStr"/>
+      <c r="AC310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -30233,6 +31387,8 @@
       <c r="AA311" t="n">
         <v>2002</v>
       </c>
+      <c r="AB311" t="inlineStr"/>
+      <c r="AC311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
@@ -30326,6 +31482,8 @@
       <c r="AA312" t="n">
         <v>1982</v>
       </c>
+      <c r="AB312" t="inlineStr"/>
+      <c r="AC312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
@@ -30419,6 +31577,8 @@
       <c r="AA313" t="n">
         <v>2003</v>
       </c>
+      <c r="AB313" t="inlineStr"/>
+      <c r="AC313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
@@ -30512,6 +31672,8 @@
       <c r="AA314" t="n">
         <v>2009</v>
       </c>
+      <c r="AB314" t="inlineStr"/>
+      <c r="AC314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
@@ -30605,6 +31767,8 @@
       <c r="AA315" t="n">
         <v>2018</v>
       </c>
+      <c r="AB315" t="inlineStr"/>
+      <c r="AC315" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Estatistica_Descritiva/df_baseED.xlsx
+++ b/Estatistica_Descritiva/df_baseED.xlsx
@@ -29953,7 +29953,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>115210</v>
+        <v>115209.66</v>
       </c>
       <c r="E282" t="n">
         <v>286.32</v>
@@ -30040,7 +30040,7 @@
         <v>3573.870786</v>
       </c>
       <c r="AC282" t="n">
-        <v>3.102049115528166</v>
+        <v>3.102058270113808</v>
       </c>
     </row>
     <row r="283">
@@ -30058,7 +30058,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>9163</v>
+        <v>9163.23</v>
       </c>
       <c r="E283" t="n">
         <v>71.72999999999999</v>
@@ -30145,7 +30145,7 @@
         <v>221.128523</v>
       </c>
       <c r="AC283" t="n">
-        <v>2.413276470588235</v>
+        <v>2.413215896577954</v>
       </c>
     </row>
     <row r="284">
@@ -30163,7 +30163,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>282628</v>
+        <v>282628.35</v>
       </c>
       <c r="E284" t="n">
         <v>4861.09</v>
@@ -30250,7 +30250,7 @@
         <v>19461.710018</v>
       </c>
       <c r="AC284" t="n">
-        <v>6.885980871675841</v>
+        <v>6.885972344246428</v>
       </c>
     </row>
     <row r="285">
@@ -30478,7 +30478,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1622418</v>
+        <v>1622418.24</v>
       </c>
       <c r="E287" t="n">
         <v>20716.82</v>
@@ -30565,7 +30565,7 @@
         <v>118476.77379</v>
       </c>
       <c r="AC287" t="n">
-        <v>7.302481468400869</v>
+        <v>7.302480388164276</v>
       </c>
     </row>
     <row r="288">
@@ -30688,7 +30688,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>56449</v>
+        <v>56448.65</v>
       </c>
       <c r="E289" t="n">
         <v>151.74</v>
@@ -30775,7 +30775,7 @@
         <v>925.5772649999999</v>
       </c>
       <c r="AC289" t="n">
-        <v>1.639669905578487</v>
+        <v>1.639680072065496</v>
       </c>
     </row>
     <row r="290">
@@ -30793,7 +30793,7 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>823845</v>
+        <v>823845.1899999999</v>
       </c>
       <c r="E290" t="n">
         <v>93.90000000000001</v>
@@ -30880,7 +30880,7 @@
         <v>867.6991480000003</v>
       </c>
       <c r="AC290" t="n">
-        <v>0.1053231066523436</v>
+        <v>0.1053230823621123</v>
       </c>
     </row>
     <row r="291">
@@ -30898,7 +30898,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>8025</v>
+        <v>8024.75</v>
       </c>
       <c r="E291" t="n">
         <v>33</v>
@@ -30985,7 +30985,7 @@
         <v>288.417291</v>
       </c>
       <c r="AC291" t="n">
-        <v>3.593984934579439</v>
+        <v>3.594096900214959</v>
       </c>
     </row>
     <row r="292">
@@ -31108,7 +31108,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>4052</v>
+        <v>4051.66</v>
       </c>
       <c r="E293" t="n">
         <v>2.39</v>
@@ -31195,7 +31195,7 @@
         <v>51.5</v>
       </c>
       <c r="AC293" t="n">
-        <v>1.270977295162883</v>
+        <v>1.271083950775731</v>
       </c>
     </row>
     <row r="294">
@@ -31213,7 +31213,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>0</v>
+        <v>11432</v>
       </c>
       <c r="E294" t="n">
         <v>1081</v>
@@ -31299,10 +31299,8 @@
       <c r="AB294" t="n">
         <v>1692.526294</v>
       </c>
-      <c r="AC294" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="AC294" t="n">
+        <v>14.80516352344297</v>
       </c>
     </row>
     <row r="295">
@@ -31320,7 +31318,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>8106.57821</v>
+        <v>8107</v>
       </c>
       <c r="E295" t="n">
         <v>112.73</v>
@@ -31407,7 +31405,7 @@
         <v>237.45</v>
       </c>
       <c r="AC295" t="n">
-        <v>2.929102684867577</v>
+        <v>2.928950289872949</v>
       </c>
     </row>
     <row r="296">
@@ -31425,7 +31423,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>14833</v>
+        <v>14833.45</v>
       </c>
       <c r="E296" t="n">
         <v>1389.18</v>
@@ -31512,7 +31510,7 @@
         <v>1631.11555</v>
       </c>
       <c r="AC296" t="n">
-        <v>10.99653171981393</v>
+        <v>10.99619811979007</v>
       </c>
     </row>
     <row r="297">
@@ -31530,7 +31528,7 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>12295</v>
+        <v>12294.58</v>
       </c>
       <c r="E297" t="n">
         <v>693.5</v>
@@ -31617,7 +31615,7 @@
         <v>998.76</v>
       </c>
       <c r="AC297" t="n">
-        <v>8.123302155347702</v>
+        <v>8.123579658678864</v>
       </c>
     </row>
     <row r="298">
@@ -31635,7 +31633,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>223927.393595</v>
+        <v>223927</v>
       </c>
       <c r="E298" t="n">
         <v>2.83</v>
@@ -31722,7 +31720,7 @@
         <v>98.39</v>
       </c>
       <c r="AC298" t="n">
-        <v>0.04393834913201835</v>
+        <v>0.04393842636216267</v>
       </c>
     </row>
   </sheetData>
